--- a/data/prediction_examples.xlsx
+++ b/data/prediction_examples.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9735"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="25">
   <si>
     <t>Ваш возраст (полных лет)?</t>
   </si>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>Был ли кариес у ваших родителей?</t>
-  </si>
-  <si>
-    <t>Сумма баллов</t>
   </si>
   <si>
     <t>Группа риска</t>
@@ -99,12 +96,21 @@
 Применение зубных флосс
 Контроль каждые 3 месяца</t>
   </si>
+  <si>
+    <t>рН вашей слюны  (по результатам анализа)</t>
+  </si>
+  <si>
+    <t>5 и более</t>
+  </si>
+  <si>
+    <t>5 и  более</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +154,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -194,7 +208,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -226,9 +240,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -260,6 +275,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -435,14 +451,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -462,22 +478,22 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
       <c r="L1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="105">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -494,28 +510,28 @@
         <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="I2" s="1">
         <v>0.1</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="105">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -532,28 +548,28 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="I3" s="1">
         <v>0.2</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="105">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -570,28 +586,28 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>6.6</v>
       </c>
       <c r="I4" s="1">
         <v>0.1</v>
       </c>
       <c r="J4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="105">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -608,28 +624,28 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I5" s="1">
         <v>0.2</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="120">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="120" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -646,28 +662,28 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="1">
         <v>0.3</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="120">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="120" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -684,28 +700,28 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I7" s="1">
         <v>0.3</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="120">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -722,28 +738,28 @@
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>23</v>
       </c>
       <c r="I8" s="1">
         <v>0.4</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="105">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -760,28 +776,28 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
       </c>
       <c r="I9" s="1">
         <v>0.5</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -798,28 +814,28 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
       </c>
       <c r="I10" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -836,28 +852,28 @@
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
       </c>
       <c r="I11" s="1">
         <v>0.6</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -874,28 +890,28 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12">
-        <v>11</v>
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>23</v>
       </c>
       <c r="I12" s="1">
         <v>0.62</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -912,28 +928,28 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
       </c>
       <c r="I13" s="1">
         <v>0.63</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -950,28 +966,28 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="H14" t="s">
+        <v>23</v>
       </c>
       <c r="I14" s="1">
         <v>0.64</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -988,28 +1004,28 @@
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="H15" t="s">
+        <v>23</v>
       </c>
       <c r="I15" s="1">
         <v>0.65</v>
       </c>
       <c r="J15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1026,28 +1042,28 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
       </c>
       <c r="I16" s="1">
         <v>0.66</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1064,28 +1080,28 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="H17" t="s">
+        <v>23</v>
       </c>
       <c r="I17" s="1">
         <v>0.67</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1102,28 +1118,28 @@
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18">
-        <v>17</v>
+        <v>11</v>
+      </c>
+      <c r="H18" t="s">
+        <v>23</v>
       </c>
       <c r="I18" s="1">
         <v>0.7</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1140,28 +1156,28 @@
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="H19" t="s">
+        <v>23</v>
       </c>
       <c r="I19" s="1">
         <v>0.8</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1178,28 +1194,28 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20">
-        <v>19</v>
+        <v>11</v>
+      </c>
+      <c r="H20" t="s">
+        <v>23</v>
       </c>
       <c r="I20" s="1">
         <v>0.9</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1216,28 +1232,28 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="H21" t="s">
+        <v>23</v>
       </c>
       <c r="I21" s="1">
         <v>0.95</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1254,28 +1270,28 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H22">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="H22" t="s">
+        <v>23</v>
       </c>
       <c r="I22" s="1">
         <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1292,28 +1308,28 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23">
-        <v>22</v>
+        <v>11</v>
+      </c>
+      <c r="H23" t="s">
+        <v>23</v>
       </c>
       <c r="I23" s="1">
         <v>0.21</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1330,28 +1346,28 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24">
+        <v>11</v>
+      </c>
+      <c r="H24" t="s">
         <v>23</v>
       </c>
       <c r="I24" s="1">
         <v>0.22</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1368,28 +1384,28 @@
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25">
-        <v>24</v>
+        <v>11</v>
+      </c>
+      <c r="H25" t="s">
+        <v>23</v>
       </c>
       <c r="I25" s="1">
         <v>0.23</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1406,28 +1422,28 @@
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26">
-        <v>25</v>
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>23</v>
       </c>
       <c r="I26" s="1">
         <v>0.24</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1444,28 +1460,28 @@
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
       </c>
       <c r="I27" s="1">
         <v>0.3</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1482,28 +1498,28 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28">
-        <v>27</v>
+        <v>11</v>
+      </c>
+      <c r="H28" t="s">
+        <v>23</v>
       </c>
       <c r="I28" s="1">
         <v>0.31</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1520,28 +1536,28 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H29">
-        <v>28</v>
+        <v>11</v>
+      </c>
+      <c r="H29" t="s">
+        <v>23</v>
       </c>
       <c r="I29" s="1">
         <v>0.4</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1558,28 +1574,28 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
-      </c>
-      <c r="H30">
-        <v>29</v>
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
+        <v>23</v>
       </c>
       <c r="I30" s="1">
         <v>0.45</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1596,28 +1612,28 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>23</v>
       </c>
       <c r="I31" s="1">
         <v>0.48</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1634,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H32">
-        <v>31</v>
+        <v>11</v>
+      </c>
+      <c r="H32" t="s">
+        <v>23</v>
       </c>
       <c r="I32" s="1">
         <v>0.49</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1672,28 +1688,28 @@
         <v>0</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>12</v>
-      </c>
-      <c r="H33">
-        <v>32</v>
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>23</v>
       </c>
       <c r="I33" s="1">
         <v>0.49</v>
       </c>
       <c r="J33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1710,28 +1726,28 @@
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H34">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>23</v>
       </c>
       <c r="I34" s="1">
         <v>0.5</v>
       </c>
       <c r="J34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1748,28 +1764,28 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H35">
-        <v>34</v>
+        <v>11</v>
+      </c>
+      <c r="H35" t="s">
+        <v>23</v>
       </c>
       <c r="I35" s="1">
         <v>0.52</v>
       </c>
       <c r="J35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1786,28 +1802,28 @@
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
-      </c>
-      <c r="H36">
-        <v>35</v>
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>23</v>
       </c>
       <c r="I36" s="1">
         <v>0.6</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1824,28 +1840,28 @@
         <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37">
-        <v>36</v>
+        <v>11</v>
+      </c>
+      <c r="H37" t="s">
+        <v>23</v>
       </c>
       <c r="I37" s="1">
         <v>0.65</v>
       </c>
       <c r="J37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1862,28 +1878,28 @@
         <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
-      </c>
-      <c r="H38">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="H38" t="s">
+        <v>23</v>
       </c>
       <c r="I38" s="1">
         <v>0.7</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1900,28 +1916,28 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39">
-        <v>38</v>
+        <v>11</v>
+      </c>
+      <c r="H39" t="s">
+        <v>23</v>
       </c>
       <c r="I39" s="1">
         <v>0.8</v>
       </c>
       <c r="J39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1938,28 +1954,28 @@
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G40" t="s">
-        <v>12</v>
-      </c>
-      <c r="H40">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="H40" t="s">
+        <v>23</v>
       </c>
       <c r="I40" s="1">
         <v>0.85</v>
       </c>
       <c r="J40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1976,28 +1992,28 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>12</v>
-      </c>
-      <c r="H41">
-        <v>40</v>
+        <v>11</v>
+      </c>
+      <c r="H41" t="s">
+        <v>23</v>
       </c>
       <c r="I41" s="1">
         <v>0.9</v>
       </c>
       <c r="J41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2014,28 +2030,28 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
-      </c>
-      <c r="H42">
-        <v>41</v>
+        <v>11</v>
+      </c>
+      <c r="H42" t="s">
+        <v>23</v>
       </c>
       <c r="I42" s="1">
         <v>0.91</v>
       </c>
       <c r="J42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2052,28 +2068,28 @@
         <v>2</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
-      </c>
-      <c r="H43">
-        <v>42</v>
+        <v>11</v>
+      </c>
+      <c r="H43" t="s">
+        <v>23</v>
       </c>
       <c r="I43" s="1">
         <v>0.95</v>
       </c>
       <c r="J43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2090,28 +2106,28 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="H44" t="s">
+        <v>23</v>
       </c>
       <c r="I44" s="1">
         <v>0.95</v>
       </c>
       <c r="J44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2128,28 +2144,28 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>12</v>
-      </c>
-      <c r="H45">
-        <v>44</v>
+        <v>11</v>
+      </c>
+      <c r="H45" t="s">
+        <v>23</v>
       </c>
       <c r="I45" s="1">
         <v>0.96</v>
       </c>
       <c r="J45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2166,28 +2182,28 @@
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
-      </c>
-      <c r="H46">
-        <v>45</v>
+        <v>11</v>
+      </c>
+      <c r="H46" t="s">
+        <v>23</v>
       </c>
       <c r="I46" s="1">
         <v>0.97</v>
       </c>
       <c r="J46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2204,28 +2220,28 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>12</v>
-      </c>
-      <c r="H47">
-        <v>46</v>
+        <v>11</v>
+      </c>
+      <c r="H47" t="s">
+        <v>23</v>
       </c>
       <c r="I47" s="1">
         <v>0.98</v>
       </c>
       <c r="J47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2242,28 +2258,28 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
-      </c>
-      <c r="H48">
-        <v>47</v>
+        <v>11</v>
+      </c>
+      <c r="H48" t="s">
+        <v>23</v>
       </c>
       <c r="I48" s="1">
         <v>0.98</v>
       </c>
       <c r="J48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2280,28 +2296,28 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H49">
-        <v>48</v>
+        <v>11</v>
+      </c>
+      <c r="H49" t="s">
+        <v>23</v>
       </c>
       <c r="I49" s="1">
         <v>0.98</v>
       </c>
       <c r="J49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2318,28 +2334,28 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
-        <v>12</v>
-      </c>
-      <c r="H50">
-        <v>49</v>
+        <v>11</v>
+      </c>
+      <c r="H50" t="s">
+        <v>23</v>
       </c>
       <c r="I50" s="1">
         <v>0.99</v>
       </c>
       <c r="J50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="105">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="105" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2356,25 +2372,25 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51">
-        <v>50</v>
+        <v>11</v>
+      </c>
+      <c r="H51" t="s">
+        <v>23</v>
       </c>
       <c r="I51" s="1">
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -2384,9 +2400,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
@@ -2394,9 +2410,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
